--- a/fundraiser_forms/010_job_training_donation_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/010_job_training_donation_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,14 +551,10 @@
           <t>Donor Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Name of donor</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -581,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -604,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -627,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -647,14 +643,10 @@
           <t>Donation Description</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Brief description of the project</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -697,11 +689,7 @@
           <t>Frequency of Donations</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Choose how often donor wants to give</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -747,14 +735,10 @@
           <t>Time of Donation</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Time of donation in 24 hour format</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -774,14 +758,10 @@
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Phone number of donor</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -867,14 +847,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Donor ID</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ID of Donor</t>
-        </is>
-      </c>
+          <t>Donor Type</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -884,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -894,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -922,190 +898,6 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>user_input_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>user_input_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Frequency of Donations</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>user_input_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Donation Method</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>user_input_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Payment Status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>user_input_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Donor Type</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>user_input_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Donor Type</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>user_input_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Donor Type</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>user_input_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Donor Type</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1122,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>job_training_program_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Job Training Program 1</t>
         </is>
       </c>
     </row>
@@ -1172,454 +964,267 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>job_training_program_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Job Training Program 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>user_input_8_choices</t>
+          <t>user_input_7_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>job_training_program_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Job Training Program 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_input_8_choices</t>
+          <t>user_input_7_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>job_training_program_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Job Training Program 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_input_13_choices</t>
+          <t>user_input_8_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_input_13_choices</t>
+          <t>user_input_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>user_input_14_choices</t>
+          <t>user_input_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>user_input_14_choices</t>
+          <t>user_input_13_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>user_input_15_choices</t>
+          <t>user_input_13_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>user_input_15_choices</t>
+          <t>user_input_14_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>user_input_17_choices</t>
+          <t>user_input_14_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>user_input_17_choices</t>
+          <t>user_input_15_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>user_input_18_choices</t>
+          <t>user_input_15_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>user_input_18_choices</t>
+          <t>user_input_16_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>user_input_19_choices</t>
+          <t>user_input_16_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>user_input_19_choices</t>
+          <t>user_input_17_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>user_input_20_choices</t>
+          <t>user_input_17_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>user_input_20_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>user_input_21_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>user_input_21_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>user_input_22_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>user_input_22_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>user_input_23_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>user_input_23_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>user_input_24_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>user_input_24_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>user_input_25_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>user_input_25_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
